--- a/src/maykr/assets/template.xlsx
+++ b/src/maykr/assets/template.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dhauck/Documents/programs/python/maykr/src/maykr/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D185659-C7A0-0846-AD72-4E6BBDEE8784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D7BA8A-6DC6-0B45-AD4E-48C901041938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Entity Details" sheetId="1" r:id="rId1"/>
+    <sheet name="Company Data" sheetId="1" r:id="rId1"/>
     <sheet name="New Addresses" sheetId="2" r:id="rId2"/>
+    <sheet name="Individuals" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -34,10 +35,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -414,7 +411,25 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32DB0757-1C59-8F4D-815D-9984BFC92B2C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="db200ba3-26d8-4305-a8e5-0023754cee81">
@@ -424,7 +439,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B146BDC91A60B4B8F01C246368D66E5" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5181daf04c6510e97871b5c687e8fa75">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db200ba3-26d8-4305-a8e5-0023754cee81" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df5f0eef1d8306fed409f1e8c19cec3a" ns2:_="">
     <xsd:import namespace="db200ba3-26d8-4305-a8e5-0023754cee81"/>
@@ -596,16 +611,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E543921F-AA80-499B-BF7B-45C4624EEDE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6581A98-3E30-4C1C-BA6A-6BBC557A45B8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -615,7 +629,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E30E6C4E-50FB-45F9-AD34-436978A34C94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -631,12 +645,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E543921F-AA80-499B-BF7B-45C4624EEDE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>